--- a/Supplier_Transition.xlsx
+++ b/Supplier_Transition.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RM Planning\Digitization\RM 8 Reasons\New 8 Reasons Tool\Actual Run 27th Nov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RM Planning\Digitization\RM 8 Reasons\New 8 Reasons Tool\SATL Nov25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C6EE97-8F01-4F57-A81E-D211A1B34432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5D7F65-9B59-4776-A2DA-BFAAEA58B23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$55</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,20 +31,161 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
-  <si>
-    <t>Phase-Out Supplier Code</t>
-  </si>
-  <si>
-    <t>Phase-In Supplier Code</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+  <si>
+    <t>CODE1171</t>
+  </si>
+  <si>
+    <t>CODE4</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>Transit Time</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Transit Time Std. Dev. (%)</t>
+  </si>
+  <si>
+    <t>JH</t>
+  </si>
+  <si>
+    <t>CODE228</t>
+  </si>
+  <si>
+    <t>CODE405</t>
+  </si>
+  <si>
+    <t>CODE510</t>
+  </si>
+  <si>
+    <t>CODE599</t>
+  </si>
+  <si>
+    <t>CODE630</t>
+  </si>
+  <si>
+    <t>KARSO</t>
+  </si>
+  <si>
+    <t>NAPLO</t>
+  </si>
+  <si>
+    <t>SARDINE</t>
+  </si>
+  <si>
+    <t>BETHUNIC</t>
+  </si>
+  <si>
+    <t>CODE1044</t>
+  </si>
+  <si>
+    <t>CODE1144</t>
+  </si>
+  <si>
+    <t>LUMTINE</t>
+  </si>
+  <si>
+    <t>MILNIC</t>
+  </si>
+  <si>
+    <t>MULTRAX</t>
+  </si>
+  <si>
+    <t>STERAX</t>
+  </si>
+  <si>
+    <t>ZONFLAX</t>
+  </si>
+  <si>
+    <t>OLIVAX</t>
+  </si>
+  <si>
+    <t>NANESIC (ML-7053)</t>
+  </si>
+  <si>
+    <t>ML2036</t>
+  </si>
+  <si>
+    <t>CODE , TRANSPARENT EVA BAG (BLUTRIC)</t>
+  </si>
+  <si>
+    <t>CODE , BLUTRIC</t>
+  </si>
+  <si>
+    <t>BINIC</t>
+  </si>
+  <si>
+    <t>COMODIC</t>
+  </si>
+  <si>
+    <t>CHEFFIC</t>
+  </si>
+  <si>
+    <t>CODE1011</t>
+  </si>
+  <si>
+    <t>KORNATIC</t>
+  </si>
+  <si>
+    <t>RENARDIC</t>
+  </si>
+  <si>
+    <t>Boehnite</t>
+  </si>
+  <si>
+    <t>Sydnine</t>
+  </si>
+  <si>
+    <t>Bijinic</t>
+  </si>
+  <si>
+    <t>CK ( Replacement for UK160)</t>
+  </si>
+  <si>
+    <t>TU32CX 1300D</t>
+  </si>
+  <si>
+    <t>TC28CX ( Pink DIP)</t>
+  </si>
+  <si>
+    <t>RIONIC
+RIL: Bromobutyl</t>
+  </si>
+  <si>
+    <t>CORMANIC 
+(BUD1208 Repl
+RIL PBR Nickel)</t>
+  </si>
+  <si>
+    <t>EVRIC (Tire to Foam) (Sup name Loctite SI 5930 FIT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THRACIC (Sup Mat Name : simalfa -3097) </t>
+  </si>
+  <si>
+    <t>Lutrabond</t>
+  </si>
+  <si>
+    <t>CODE-CROYDAX</t>
+  </si>
+  <si>
+    <t>BLACK  M-3902 SAKAIKAGAKU- MAKE</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>I-47-LZ-NY CHAFER FABRIC</t>
   </si>
   <si>
     <t>Plant Code</t>
@@ -54,22 +198,166 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -78,12 +366,197 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-        <bgColor rgb="FFFF8080"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -92,103 +565,266 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFED7D31"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -201,9 +837,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,44 +847,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -276,31 +912,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -328,26 +947,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -356,277 +958,1309 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1100658</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5">
+        <v>114766</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1100175</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>150136</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1100174</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>150136</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1100172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>150136</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1100219</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="14">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5">
+        <v>150136</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1100173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>150136</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1100172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>147571</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1100175</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>147571</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1100172</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>149508</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1100174</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>149508</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1100946</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <f>5-2</f>
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>149500</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1100520</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <f>5-2</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>114735</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1100520</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <f>10-2</f>
+        <v>8</v>
+      </c>
+      <c r="D14" s="5">
+        <v>150417</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1101667</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>114759</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1101667</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>677252</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1100935</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>113283</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1100070</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <f>4+1</f>
+        <v>5</v>
+      </c>
+      <c r="D18" s="5">
+        <v>114761</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1100076</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5">
+        <v>149425</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1100032</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="5">
+        <v>113216</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1102664</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5">
+        <v>143977</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1101020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" s="5">
+        <v>116582</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1100491</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5">
+        <v>116582</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1100058</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>114754</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1100041</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <f>4-1</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="5">
+        <v>113293</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1100195</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" s="5">
+        <v>113293</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1100041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27">
+        <f>4-1</f>
+        <v>3</v>
+      </c>
+      <c r="D27" s="5">
+        <v>148822</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1100195</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" s="5">
+        <v>148822</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1100029</v>
+      </c>
+      <c r="B29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C29">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="D29" s="5">
+        <v>114737</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1102615</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>204053</v>
-      </c>
-      <c r="B2">
-        <v>200562</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D30" s="5">
+        <v>113254</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1102660</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5">
+        <v>113254</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1101803</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5">
+        <v>618179</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1101569</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33" s="5">
+        <v>618179</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1100287</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="D34" s="5">
+        <v>149137</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1100765</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="D35" s="5">
+        <v>149137</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1101287</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="D36" s="5">
+        <v>149137</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1100194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37">
+        <f>5-2</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>204220</v>
-      </c>
-      <c r="B3">
-        <v>200562</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D37" s="5">
+        <v>149794</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1100194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <f>6-2</f>
+        <v>4</v>
+      </c>
+      <c r="D38" s="5">
+        <v>113279</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1102444</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>204074</v>
-      </c>
-      <c r="B4">
-        <v>204119</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D39" s="6">
+        <v>90009513</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1100046</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>203089</v>
-      </c>
-      <c r="B5">
-        <v>633589</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D40" s="6">
+        <v>90009513</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1100765</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41">
+        <f>5+1</f>
+        <v>6</v>
+      </c>
+      <c r="D41" s="5">
+        <v>146809</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1101441</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" s="5">
+        <v>622806</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1100687</v>
+      </c>
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5">
+        <v>90000858</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1100690</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5">
+        <v>676620</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1100991</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="D45" s="5">
+        <v>90002638</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1102277</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" s="7">
+        <v>90010204</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1102438</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" s="7">
+        <v>90010204</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1100098</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48">
+        <f>4+1</f>
+        <v>5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>90003023</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1101860</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49" s="5">
+        <v>149137</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1102101</v>
+      </c>
+      <c r="B50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>617948</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1102102</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" s="5">
+        <v>90018362</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1100994</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>204145</v>
-      </c>
-      <c r="B6">
+      <c r="D52" s="5">
+        <v>677209</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1100040</v>
+      </c>
+      <c r="B53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53" s="5">
         <v>622806</v>
       </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>202105</v>
-      </c>
-      <c r="B7">
-        <v>632835</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>201704</v>
-      </c>
-      <c r="B8">
-        <v>200562</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>204053</v>
-      </c>
-      <c r="B9">
-        <v>90010204</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>201761</v>
-      </c>
-      <c r="B10">
-        <v>90010204</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
+      <c r="E53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1101040</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" s="5">
+        <v>146885</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9">
+        <v>1101000</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" s="9">
+        <v>2</v>
+      </c>
+      <c r="D55" s="10">
+        <v>113215</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
+  <autoFilter ref="A1:E55" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D3">
+    <sortCondition ref="A3"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -635,7 +2269,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FE90F4C888C3E247BAF35D2B4D0C4B01" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b74c3fcc9b2d4b486f41b9af1c8eb7a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1525da01-8289-4adf-9aef-155ddab9de1b" xmlns:ns3="f1836e8f-289b-491c-9556-67e7084501af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4359aa3c0acb601a6d2eef82da988ac2" ns2:_="" ns3:_="">
     <xsd:import namespace="1525da01-8289-4adf-9aef-155ddab9de1b"/>
@@ -812,23 +2446,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D268980-8340-4A04-8B78-307314C8231A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5685F56D-7802-40D4-8FA5-0E79ADE7E5BE}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E2C815-9FE1-414C-B7CB-2036FD98E530}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C802447-6286-42BB-A7C9-4AC73D9C2775}"/>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B44C3916-F4AE-440A-BD29-1F2F7EB6EC6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C29A9CC-DE79-4E75-A96A-EAC90AF56684}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>